--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,40 +28,19 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20048847</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP900</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
   </si>
 </sst>
 </file>
@@ -454,13 +433,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,46 +500,6 @@
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,19 +28,28 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ LVNDR 510</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT VIOLET 1.5</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -433,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -502,6 +511,26 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20141369</t>
-  </si>
-  <si>
-    <t>RINSO P.BRZE BTL 650</t>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ LVNDR 510</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
   </si>
   <si>
     <t>2</t>
@@ -43,10 +43,10 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
   </si>
   <si>
     <t>3</t>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,28 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>10003272</t>
+  </si>
+  <si>
+    <t>BAYGON SPRY CITRS675</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -442,13 +451,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -508,15 +517,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +534,30 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t/>
   </si>
   <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
+    <t>20135245</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ FRNCH700</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -31,31 +31,28 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
+    <t>20133798</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ EN.RS700</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>10003272</t>
-  </si>
-  <si>
-    <t>BAYGON SPRY CITRS675</t>
+    <t>20134526</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG COT.FN780</t>
   </si>
   <si>
     <t>4</t>
@@ -457,7 +454,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -537,15 +534,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -554,10 +551,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135245</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ FRNCH700</t>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF770</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -31,28 +31,31 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20133798</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ EN.RS700</t>
+    <t>10003646</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L APPLE770</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20134526</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG COT.FN780</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
     <t>4</t>
@@ -534,15 +537,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -551,10 +554,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF770</t>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,37 +28,31 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10003646</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L APPLE770</t>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>RT,(E-3.5B)</t>
   </si>
 </sst>
 </file>
@@ -451,13 +445,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -517,15 +511,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -534,30 +528,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,31 +28,28 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20054747</t>
+  </si>
+  <si>
+    <t>SO KLIN VL/BLSOM 700</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20067585</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ RED SB 700</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +448,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -531,7 +528,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20054747</t>
-  </si>
-  <si>
-    <t>SO KLIN VL/BLSOM 700</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT VIOLET 1.5</t>
   </si>
   <si>
     <t>2</t>
@@ -43,13 +43,16 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20067585</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ RED SB 700</t>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -528,7 +531,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
+    <t>10011440</t>
+  </si>
+  <si>
+    <t>RAPIKA LVDR SPLAS300</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,31 +28,28 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20120180</t>
+  </si>
+  <si>
+    <t>SO SOFT RS&amp;WTRLY 700</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +448,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -511,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -528,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>10011440</t>
-  </si>
-  <si>
-    <t>RAPIKA LVDR SPLAS300</t>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,28 +28,28 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20120180</t>
-  </si>
-  <si>
-    <t>SO SOFT RS&amp;WTRLY 700</t>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20093521</t>
-  </si>
-  <si>
-    <t>RINSO+MOLTO ESC1440G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -508,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141204</t>
-  </si>
-  <si>
-    <t>IDM P.PRG JR.NPS 950</t>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,28 +28,49 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20139947</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 675G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -442,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -508,15 +529,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +546,50 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,66 +11,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
+  </si>
+  <si>
+    <t>DU1BMKT</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
     <t>10013205</t>
   </si>
   <si>
     <t>SUNLIGHT J/NIPIS.750</t>
   </si>
   <si>
-    <t>DU1BMKT</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>2</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20139947</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 675G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
+    <t>20071775</t>
+  </si>
+  <si>
+    <t>BAYGON FLO.GRDN 675</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>RT,(E-3.5B)</t>
   </si>
 </sst>
 </file>
@@ -463,13 +445,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -529,15 +511,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -546,50 +528,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
+    <t>20052321</t>
+  </si>
+  <si>
+    <t>DAIA SFT PINK 1.5 KG</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,31 +28,31 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENGEN DECA M 700 ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20071775</t>
-  </si>
-  <si>
-    <t>BAYGON FLO.GRDN 675</t>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA +SFT VLT 1.5 KG</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-3.5B)</t>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENGEN DECASI 700 ML</t>
   </si>
 </sst>
 </file>
@@ -445,13 +445,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -511,15 +511,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -528,10 +528,30 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20052321</t>
-  </si>
-  <si>
-    <t>DAIA SFT PINK 1.5 KG</t>
+    <t>20064413</t>
+  </si>
+  <si>
+    <t>ATCK JAZ1 S/CNTA 1.5</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -28,31 +28,28 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENGEN DECA M 700 ML</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA +SFT VLT 1.5 KG</t>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 600</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENGEN DECASI 700 ML</t>
   </si>
 </sst>
 </file>
@@ -445,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -511,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -528,30 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -16,40 +16,40 @@
     <t/>
   </si>
   <si>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ LVNDR 510</t>
+  </si>
+  <si>
+    <t>DU1BMKT</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ SAKURA 510</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>20064413</t>
   </si>
   <si>
     <t>ATCK JAZ1 S/CNTA 1.5</t>
   </si>
   <si>
-    <t>DU1BMKT</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>RT</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 600</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 600</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -508,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="12">
   <si>
     <t/>
   </si>
   <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ LVNDR 510</t>
+    <t>20099414</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT PRPL1.3</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -31,25 +31,22 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20093627</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ SAKURA 510</t>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20064413</t>
-  </si>
-  <si>
-    <t>ATCK JAZ1 S/CNTA 1.5</t>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -442,16 +439,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,8 +468,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -487,11 +491,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -507,11 +511,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -527,8 +531,8 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
+      <c r="H4" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20099414</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT PRPL1.3</t>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -31,19 +31,22 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20113567</t>
   </si>
   <si>
     <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
   </si>
   <si>
     <t>3</t>
@@ -439,17 +442,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,14 +470,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -491,11 +487,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -511,16 +507,16 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -529,9 +525,9 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
+    <t>20061748</t>
+  </si>
+  <si>
+    <t>DAIA PWDR VLT PSN725</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -31,25 +31,13 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
+    <t>20036047</t>
+  </si>
+  <si>
+    <t>DAIA PWDR ROM/PNK725</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -442,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -508,26 +496,6 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU1BMKT.xlsx
+++ b/E/DU1BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t/>
   </si>
   <si>
-    <t>20061748</t>
-  </si>
-  <si>
-    <t>DAIA PWDR VLT PSN725</t>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SKLN LQD SKR STRW500</t>
   </si>
   <si>
     <t>DU1BMKT</t>
@@ -31,13 +31,31 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20036047</t>
-  </si>
-  <si>
-    <t>DAIA PWDR ROM/PNK725</t>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SKLN LQD PROV LVD500</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
   </si>
 </sst>
 </file>
@@ -430,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -499,6 +517,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
